--- a/Škola_bc.xlsx
+++ b/Škola_bc.xlsx
@@ -1,25 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ardno\Downloads\Škola\Bakalarske\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48C62BAF-90BC-40F1-A7F2-32FF957BF865}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300"/>
+    <workbookView xWindow="14370" yWindow="0" windowWidth="14535" windowHeight="15585" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Povinné" sheetId="2" r:id="rId1"/>
     <sheet name="PVA" sheetId="4" r:id="rId2"/>
     <sheet name="PVB" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -688,8 +703,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="7" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -748,6 +763,13 @@
       <b/>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="238"/>
@@ -910,6 +932,326 @@
   </cellStyles>
   <dxfs count="49">
     <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1100,164 +1442,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1334,172 +1518,10 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1515,149 +1537,149 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="16" name="Tabulka117" displayName="Tabulka117" ref="A2:G39" totalsRowShown="0" headerRowDxfId="46">
-  <autoFilter ref="A2:G39"/>
-  <sortState ref="A3:G39">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="16" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabulka117" displayName="Tabulka117" ref="A2:G39" totalsRowShown="0" headerRowDxfId="48">
+  <autoFilter ref="A2:G39" xr:uid="{00000000-0009-0000-0100-000010000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:G39">
     <sortCondition ref="A2:A39"/>
   </sortState>
   <tableColumns count="7">
-    <tableColumn id="1" name="Semestr"/>
-    <tableColumn id="2" name="Kód" dataDxfId="45" dataCellStyle="Hypertextový odkaz"/>
-    <tableColumn id="3" name="Název" dataCellStyle="Normální"/>
-    <tableColumn id="4" name="Kredity"/>
-    <tableColumn id="5" name="Ukončení"/>
-    <tableColumn id="6" name="Typ ukončení"/>
-    <tableColumn id="7" name="Status"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Semestr"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Kód" dataDxfId="47" dataCellStyle="Hypertextový odkaz"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Název" dataCellStyle="Normální"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Kredity"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Ukončení"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Typ ukončení"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Status"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="Tabulka220" displayName="Tabulka220" ref="A2:G6" totalsRowShown="0" headerRowDxfId="40" headerRowBorderDxfId="39" tableBorderDxfId="38">
-  <autoFilter ref="A2:G6"/>
-  <sortState ref="A3:G6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="19" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Tabulka220" displayName="Tabulka220" ref="A2:G6" totalsRowShown="0" headerRowDxfId="46" headerRowBorderDxfId="45" tableBorderDxfId="44">
+  <autoFilter ref="A2:G6" xr:uid="{00000000-0009-0000-0100-000013000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:G6">
     <sortCondition ref="A3:A7"/>
   </sortState>
   <tableColumns count="7">
-    <tableColumn id="1" name="Semestr" dataDxfId="37"/>
-    <tableColumn id="2" name="Kód" dataDxfId="36" dataCellStyle="Hypertextový odkaz"/>
-    <tableColumn id="3" name="Název"/>
-    <tableColumn id="4" name="Kredity"/>
-    <tableColumn id="5" name="Ukončení"/>
-    <tableColumn id="6" name="Typ ukončení"/>
-    <tableColumn id="7" name="Status"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Semestr" dataDxfId="43"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Kód" dataDxfId="42" dataCellStyle="Hypertextový odkaz"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Název"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="Kredity"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="Ukončení"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Typ ukončení"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Status"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="Tabulka321" displayName="Tabulka321" ref="A15:G18" totalsRowShown="0" headerRowDxfId="35" headerRowBorderDxfId="34" tableBorderDxfId="33">
-  <autoFilter ref="A15:G18"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="20" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Tabulka321" displayName="Tabulka321" ref="A15:G18" totalsRowShown="0" headerRowDxfId="41" headerRowBorderDxfId="40" tableBorderDxfId="39">
+  <autoFilter ref="A15:G18" xr:uid="{00000000-0009-0000-0100-000014000000}"/>
   <tableColumns count="7">
-    <tableColumn id="1" name="Semestr" dataDxfId="32"/>
-    <tableColumn id="2" name="Kód" dataDxfId="31" dataCellStyle="Hypertextový odkaz"/>
-    <tableColumn id="3" name="Název"/>
-    <tableColumn id="4" name="Kredity"/>
-    <tableColumn id="5" name="Ukončení"/>
-    <tableColumn id="6" name="Typ ukončení"/>
-    <tableColumn id="7" name="Status"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Semestr" dataDxfId="38"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Kód" dataDxfId="37" dataCellStyle="Hypertextový odkaz"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Název"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="Kredity"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Ukončení"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Typ ukončení"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="Status"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="23" name="Tabulka22024" displayName="Tabulka22024" ref="A2:G8" totalsRowShown="0" headerRowDxfId="24" headerRowBorderDxfId="23" tableBorderDxfId="22">
-  <autoFilter ref="A2:G8"/>
-  <sortState ref="A3:G8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="23" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="Tabulka22024" displayName="Tabulka22024" ref="A2:G8" totalsRowShown="0" headerRowDxfId="36" headerRowBorderDxfId="35" tableBorderDxfId="34">
+  <autoFilter ref="A2:G8" xr:uid="{00000000-0009-0000-0100-000017000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:G8">
     <sortCondition ref="B2:B8"/>
   </sortState>
   <tableColumns count="7">
-    <tableColumn id="1" name="Semestr" dataDxfId="21"/>
-    <tableColumn id="2" name="Kód" dataDxfId="20" dataCellStyle="Hypertextový odkaz"/>
-    <tableColumn id="3" name="Název"/>
-    <tableColumn id="4" name="Kredity"/>
-    <tableColumn id="5" name="Ukončení"/>
-    <tableColumn id="6" name="Typ ukončení"/>
-    <tableColumn id="7" name="Status"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Semestr" dataDxfId="33"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Kód" dataDxfId="32" dataCellStyle="Hypertextový odkaz"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Název"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="Kredity"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="Ukončení"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="Typ ukončení"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0300-000007000000}" name="Status"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Tabulka220245" displayName="Tabulka220245" ref="A15:G20" totalsRowShown="0" headerRowDxfId="19" headerRowBorderDxfId="18" tableBorderDxfId="17">
-  <autoFilter ref="A15:G20"/>
-  <sortState ref="A16:G21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Tabulka220245" displayName="Tabulka220245" ref="A15:G20" totalsRowShown="0" headerRowDxfId="31" headerRowBorderDxfId="30" tableBorderDxfId="29">
+  <autoFilter ref="A15:G20" xr:uid="{00000000-0009-0000-0100-000004000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A16:G21">
     <sortCondition ref="A2:A8"/>
   </sortState>
   <tableColumns count="7">
-    <tableColumn id="1" name="Semestr" dataDxfId="16"/>
-    <tableColumn id="2" name="Kód" dataDxfId="15" dataCellStyle="Hypertextový odkaz"/>
-    <tableColumn id="3" name="Název"/>
-    <tableColumn id="4" name="Kredity"/>
-    <tableColumn id="5" name="Ukončení"/>
-    <tableColumn id="6" name="Typ ukončení"/>
-    <tableColumn id="7" name="Status"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="Semestr" dataDxfId="28"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Kód" dataDxfId="27" dataCellStyle="Hypertextový odkaz"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="Název"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="Kredity"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" name="Ukončení"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0400-000006000000}" name="Typ ukončení"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0400-000007000000}" name="Status"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Tabulka2202456" displayName="Tabulka2202456" ref="A27:G38" totalsRowShown="0" headerRowDxfId="14" headerRowBorderDxfId="13" tableBorderDxfId="12" dataCellStyle="Normální">
-  <autoFilter ref="A27:G38"/>
-  <sortState ref="A28:G33">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="Tabulka2202456" displayName="Tabulka2202456" ref="A27:G38" totalsRowShown="0" headerRowDxfId="26" headerRowBorderDxfId="25" tableBorderDxfId="24" dataCellStyle="Normální">
+  <autoFilter ref="A27:G38" xr:uid="{00000000-0009-0000-0100-000005000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A28:G33">
     <sortCondition ref="A2:A8"/>
   </sortState>
   <tableColumns count="7">
-    <tableColumn id="1" name="Semestr" dataDxfId="11" dataCellStyle="Normální"/>
-    <tableColumn id="2" name="Kód" dataDxfId="10" dataCellStyle="Hypertextový odkaz"/>
-    <tableColumn id="3" name="Název" dataCellStyle="Normální"/>
-    <tableColumn id="4" name="Kredity" dataCellStyle="Normální"/>
-    <tableColumn id="5" name="Ukončení" dataCellStyle="Normální"/>
-    <tableColumn id="6" name="Typ ukončení" dataCellStyle="Normální"/>
-    <tableColumn id="7" name="Status" dataCellStyle="Normální"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="Semestr" dataDxfId="23" dataCellStyle="Normální"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="Kód" dataDxfId="22" dataCellStyle="Hypertextový odkaz"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="Název" dataCellStyle="Normální"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="Kredity" dataCellStyle="Normální"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" name="Ukončení" dataCellStyle="Normální"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="Typ ukončení" dataCellStyle="Normální"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" name="Status" dataCellStyle="Normální"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Tabulka2202457" displayName="Tabulka2202457" ref="A45:G49" totalsRowShown="0" headerRowDxfId="9" headerRowBorderDxfId="8" tableBorderDxfId="7">
-  <autoFilter ref="A45:G49"/>
-  <sortState ref="A46:G51">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="Tabulka2202457" displayName="Tabulka2202457" ref="A45:G49" totalsRowShown="0" headerRowDxfId="21" headerRowBorderDxfId="20" tableBorderDxfId="19">
+  <autoFilter ref="A45:G49" xr:uid="{00000000-0009-0000-0100-000006000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A46:G51">
     <sortCondition ref="A2:A8"/>
   </sortState>
   <tableColumns count="7">
-    <tableColumn id="1" name="Semestr" dataDxfId="6"/>
-    <tableColumn id="2" name="Kód" dataDxfId="5" dataCellStyle="Hypertextový odkaz"/>
-    <tableColumn id="3" name="Název"/>
-    <tableColumn id="4" name="Kredity"/>
-    <tableColumn id="5" name="Ukončení"/>
-    <tableColumn id="6" name="Typ ukončení"/>
-    <tableColumn id="7" name="Status"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="Semestr" dataDxfId="18"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="Kód" dataDxfId="17" dataCellStyle="Hypertextový odkaz"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" name="Název"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" name="Kredity"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0600-000005000000}" name="Ukončení"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0600-000006000000}" name="Typ ukončení"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0600-000007000000}" name="Status"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Tabulka22024568" displayName="Tabulka22024568" ref="A56:G66" totalsRowShown="0" headerRowDxfId="4" headerRowBorderDxfId="3" tableBorderDxfId="2" dataCellStyle="Normální">
-  <autoFilter ref="A56:G66"/>
-  <sortState ref="A57:G62">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF07000000}" name="Tabulka22024568" displayName="Tabulka22024568" ref="A56:G66" totalsRowShown="0" headerRowDxfId="16" headerRowBorderDxfId="15" tableBorderDxfId="14" dataCellStyle="Normální">
+  <autoFilter ref="A56:G66" xr:uid="{00000000-0009-0000-0100-000007000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A57:G62">
     <sortCondition ref="A2:A8"/>
   </sortState>
   <tableColumns count="7">
-    <tableColumn id="1" name="Semestr" dataDxfId="1" dataCellStyle="Normální"/>
-    <tableColumn id="2" name="Kód" dataDxfId="0" dataCellStyle="Hypertextový odkaz"/>
-    <tableColumn id="3" name="Název" dataCellStyle="Normální"/>
-    <tableColumn id="4" name="Kredity" dataCellStyle="Normální"/>
-    <tableColumn id="5" name="Ukončení" dataCellStyle="Normální"/>
-    <tableColumn id="6" name="Typ ukončení" dataCellStyle="Normální"/>
-    <tableColumn id="7" name="Status" dataCellStyle="Normální"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0700-000001000000}" name="Semestr" dataDxfId="13" dataCellStyle="Normální"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0700-000002000000}" name="Kód" dataDxfId="12" dataCellStyle="Hypertextový odkaz"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0700-000003000000}" name="Název" dataCellStyle="Normální"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0700-000004000000}" name="Kredity" dataCellStyle="Normální"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0700-000005000000}" name="Ukončení" dataCellStyle="Normální"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0700-000006000000}" name="Typ ukončení" dataCellStyle="Normální"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0700-000007000000}" name="Status" dataCellStyle="Normální"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1925,7 +1947,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2002,7 +2024,7 @@
       <c r="K3" s="22"/>
       <c r="L3" s="9" t="str">
         <f>COUNTIF(Tabulka117[Status],"Ano")&amp;" / "&amp;COUNTIF(Tabulka117[Status],"*")</f>
-        <v>36 / 37</v>
+        <v>7 / 37</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -2025,7 +2047,7 @@
         <v>84</v>
       </c>
       <c r="G4" t="s">
-        <v>81</v>
+        <v>198</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2048,7 +2070,7 @@
         <v>85</v>
       </c>
       <c r="G5" t="s">
-        <v>81</v>
+        <v>198</v>
       </c>
       <c r="I5" s="22" t="s">
         <v>92</v>
@@ -2057,7 +2079,7 @@
       <c r="K5" s="22"/>
       <c r="L5" s="9" t="str">
         <f>SUMIFS(Tabulka117[Kredity], Tabulka117[Status],"Ano")&amp;" / "&amp;SUM(Tabulka117[Kredity])</f>
-        <v>144 / 147</v>
+        <v>32 / 147</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
@@ -2080,7 +2102,7 @@
         <v>85</v>
       </c>
       <c r="G6" t="s">
-        <v>81</v>
+        <v>198</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
@@ -2148,7 +2170,7 @@
       <c r="F9" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="G9" t="s">
         <v>81</v>
       </c>
     </row>
@@ -2171,7 +2193,7 @@
       <c r="F10" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="G10" t="s">
         <v>81</v>
       </c>
     </row>
@@ -2194,8 +2216,8 @@
       <c r="F11" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="G11" s="6" t="s">
-        <v>198</v>
+      <c r="G11" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
@@ -2217,8 +2239,8 @@
       <c r="F12" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="G12" s="6" t="s">
-        <v>81</v>
+      <c r="G12" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
@@ -2240,7 +2262,7 @@
       <c r="F13" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="G13" s="6" t="s">
+      <c r="G13" t="s">
         <v>81</v>
       </c>
     </row>
@@ -2263,7 +2285,7 @@
       <c r="F14" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="G14" s="6" t="s">
+      <c r="G14" t="s">
         <v>81</v>
       </c>
       <c r="I14" s="22" t="s">
@@ -2293,7 +2315,7 @@
  +IFERROR(SUM(Tabulka2202457[Kredity]), 0)
  +IFERROR(SUM(Tabulka22024568[Kredity]), 0)
 )</f>
-        <v>177 / 270</v>
+        <v>46 / 270</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
@@ -2316,7 +2338,7 @@
         <v>86</v>
       </c>
       <c r="G15" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
@@ -2339,7 +2361,7 @@
         <v>84</v>
       </c>
       <c r="G16" t="s">
-        <v>81</v>
+        <v>198</v>
       </c>
       <c r="I16" s="22" t="s">
         <v>197</v>
@@ -2368,7 +2390,7 @@
 +IFERROR(SUM(Tabulka2202457[Kredity]), 0)
 +IFERROR(SUM(Tabulka22024568[Kredity]), 0)
 )</f>
-        <v>186 / 270</v>
+        <v>78 / 270</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
@@ -2391,7 +2413,7 @@
         <v>88</v>
       </c>
       <c r="G17" t="s">
-        <v>81</v>
+        <v>198</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
@@ -2414,7 +2436,7 @@
         <v>85</v>
       </c>
       <c r="G18" t="s">
-        <v>81</v>
+        <v>198</v>
       </c>
       <c r="I18" s="20"/>
       <c r="J18" s="20"/>
@@ -2440,7 +2462,7 @@
         <v>89</v>
       </c>
       <c r="G19" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
@@ -2463,7 +2485,7 @@
         <v>85</v>
       </c>
       <c r="G20" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
@@ -2486,7 +2508,7 @@
         <v>85</v>
       </c>
       <c r="G21" t="s">
-        <v>81</v>
+        <v>198</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
@@ -2509,7 +2531,7 @@
         <v>85</v>
       </c>
       <c r="G22" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
@@ -2532,7 +2554,7 @@
         <v>85</v>
       </c>
       <c r="G23" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -2555,7 +2577,7 @@
         <v>85</v>
       </c>
       <c r="G24" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -2578,7 +2600,7 @@
         <v>88</v>
       </c>
       <c r="G25" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -2601,7 +2623,7 @@
         <v>84</v>
       </c>
       <c r="G26" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
@@ -2624,7 +2646,7 @@
         <v>85</v>
       </c>
       <c r="G27" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -2647,7 +2669,7 @@
         <v>89</v>
       </c>
       <c r="G28" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -2670,7 +2692,7 @@
         <v>89</v>
       </c>
       <c r="G29" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -2693,7 +2715,7 @@
         <v>85</v>
       </c>
       <c r="G30" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -2716,7 +2738,7 @@
         <v>89</v>
       </c>
       <c r="G31" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
@@ -2739,7 +2761,7 @@
         <v>88</v>
       </c>
       <c r="G32" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -2762,7 +2784,7 @@
         <v>85</v>
       </c>
       <c r="G33" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -2785,7 +2807,7 @@
         <v>88</v>
       </c>
       <c r="G34" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -2808,7 +2830,7 @@
         <v>85</v>
       </c>
       <c r="G35" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
@@ -2831,7 +2853,7 @@
         <v>85</v>
       </c>
       <c r="G36" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -2854,7 +2876,7 @@
         <v>86</v>
       </c>
       <c r="G37" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
@@ -2877,7 +2899,7 @@
         <v>90</v>
       </c>
       <c r="G38" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
@@ -2900,7 +2922,7 @@
         <v>88</v>
       </c>
       <c r="G39" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -2911,44 +2933,45 @@
     <mergeCell ref="I14:K14"/>
     <mergeCell ref="I16:K16"/>
   </mergeCells>
+  <phoneticPr fontId="7" type="noConversion"/>
   <conditionalFormatting sqref="A3:G39">
-    <cfRule type="expression" dxfId="48" priority="1">
+    <cfRule type="expression" dxfId="11" priority="1">
       <formula>$G3="Dělám"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="47" priority="2">
+    <cfRule type="expression" dxfId="10" priority="2">
       <formula>$G3="Ano"</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="B3" r:id="rId1" display="https://is.slu.cz/auth/predmet/fpf/zima2023/UIIABP0001"/>
-    <hyperlink ref="B39" r:id="rId2" display="https://is.slu.cz/auth/predmet/fpf/leto2024/UIIABP0057"/>
-    <hyperlink ref="B38" r:id="rId3" display="https://is.slu.cz/auth/predmet/fpf/leto2024/UIIABP0056"/>
-    <hyperlink ref="B24" r:id="rId4" display="https://is.slu.cz/auth/predmet/fpf/leto2024/UIIABP0050"/>
-    <hyperlink ref="B19" r:id="rId5" display="https://is.slu.cz/auth/predmet/fpf/zima2024/UIIABP0011"/>
-    <hyperlink ref="B18" r:id="rId6" display="https://is.slu.cz/auth/predmet/fpf/zima2024/UIIABP0010"/>
-    <hyperlink ref="B17" r:id="rId7" display="https://is.slu.cz/auth/predmet/fpf/zima2024/UIIABP0009"/>
-    <hyperlink ref="B28" r:id="rId8" display="https://is.slu.cz/auth/predmet/fpf/leto2024/UIIABP0049"/>
-    <hyperlink ref="B22" r:id="rId9" display="https://is.slu.cz/auth/predmet/fpf/leto2024/UIIABP0046"/>
-    <hyperlink ref="B21" r:id="rId10" display="https://is.slu.cz/auth/predmet/fpf/zima2024/UIIABP0054"/>
-    <hyperlink ref="B20" r:id="rId11" display="https://is.slu.cz/auth/predmet/fpf/zima2024/UIIABP0012"/>
-    <hyperlink ref="B37" r:id="rId12" display="https://is.slu.cz/auth/predmet/fpf/zima2024/UIIABP0013"/>
-    <hyperlink ref="B15" r:id="rId13" display="https://is.slu.cz/auth/predmet/fpf/zima2024/UIIABP0007"/>
-    <hyperlink ref="B23" r:id="rId14" display="https://is.slu.cz/auth/predmet/fpf/leto2024/UIIABP0048"/>
-    <hyperlink ref="B35" r:id="rId15" display="https://is.slu.cz/auth/predmet/fpf/zima2024/UIIABP0019"/>
-    <hyperlink ref="B34" r:id="rId16" display="https://is.slu.cz/auth/predmet/fpf/zima2024/UIIABP0018"/>
-    <hyperlink ref="B36" r:id="rId17" display="https://is.slu.cz/auth/predmet/fpf/zima2023/UIIABP0017"/>
-    <hyperlink ref="B16" r:id="rId18" display="https://is.slu.cz/auth/predmet/fpf/zima2024/UIIABP0008"/>
-    <hyperlink ref="B14" r:id="rId19" display="https://is.slu.cz/auth/predmet/fpf/leto2024/UIIABP0047"/>
-    <hyperlink ref="B13" r:id="rId20" display="https://is.slu.cz/auth/predmet/fpf/leto2024/UIIABP0045"/>
-    <hyperlink ref="B12" r:id="rId21" display="https://is.slu.cz/auth/predmet/fpf/leto2024/UIIABP0044"/>
-    <hyperlink ref="B11" r:id="rId22" display="https://is.slu.cz/auth/predmet/fpf/leto2024/UIIABP0042"/>
-    <hyperlink ref="B10" r:id="rId23" display="https://is.slu.cz/auth/predmet/fpf/leto2024/UIIABP0042"/>
-    <hyperlink ref="B9" r:id="rId24" display="https://is.slu.cz/auth/predmet/fpf/leto2024/UIIABP0041"/>
-    <hyperlink ref="B8" r:id="rId25" display="https://is.slu.cz/auth/predmet/fpf/zima2023/UIIABP0006"/>
-    <hyperlink ref="B7" r:id="rId26" display="https://is.slu.cz/auth/predmet/fpf/zima2023/UIIABP0003"/>
-    <hyperlink ref="B6" r:id="rId27" display="https://is.slu.cz/auth/predmet/fpf/zima2023/UIIABP0003"/>
-    <hyperlink ref="B5" r:id="rId28" display="https://is.slu.cz/auth/predmet/fpf/zima2023/UIIABP0003"/>
-    <hyperlink ref="B4" r:id="rId29" display="https://is.slu.cz/auth/predmet/fpf/zima2023/UIIABP0002"/>
+    <hyperlink ref="B3" r:id="rId1" display="https://is.slu.cz/auth/predmet/fpf/zima2023/UIIABP0001" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="B39" r:id="rId2" display="https://is.slu.cz/auth/predmet/fpf/leto2024/UIIABP0057" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="B38" r:id="rId3" display="https://is.slu.cz/auth/predmet/fpf/leto2024/UIIABP0056" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="B24" r:id="rId4" display="https://is.slu.cz/auth/predmet/fpf/leto2024/UIIABP0050" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="B19" r:id="rId5" display="https://is.slu.cz/auth/predmet/fpf/zima2024/UIIABP0011" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="B18" r:id="rId6" display="https://is.slu.cz/auth/predmet/fpf/zima2024/UIIABP0010" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="B17" r:id="rId7" display="https://is.slu.cz/auth/predmet/fpf/zima2024/UIIABP0009" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="B28" r:id="rId8" display="https://is.slu.cz/auth/predmet/fpf/leto2024/UIIABP0049" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="B22" r:id="rId9" display="https://is.slu.cz/auth/predmet/fpf/leto2024/UIIABP0046" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="B21" r:id="rId10" display="https://is.slu.cz/auth/predmet/fpf/zima2024/UIIABP0054" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="B20" r:id="rId11" display="https://is.slu.cz/auth/predmet/fpf/zima2024/UIIABP0012" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="B37" r:id="rId12" display="https://is.slu.cz/auth/predmet/fpf/zima2024/UIIABP0013" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="B15" r:id="rId13" display="https://is.slu.cz/auth/predmet/fpf/zima2024/UIIABP0007" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="B23" r:id="rId14" display="https://is.slu.cz/auth/predmet/fpf/leto2024/UIIABP0048" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="B35" r:id="rId15" display="https://is.slu.cz/auth/predmet/fpf/zima2024/UIIABP0019" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="B34" r:id="rId16" display="https://is.slu.cz/auth/predmet/fpf/zima2024/UIIABP0018" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="B36" r:id="rId17" display="https://is.slu.cz/auth/predmet/fpf/zima2023/UIIABP0017" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="B16" r:id="rId18" display="https://is.slu.cz/auth/predmet/fpf/zima2024/UIIABP0008" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="B14" r:id="rId19" display="https://is.slu.cz/auth/predmet/fpf/leto2024/UIIABP0047" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="B13" r:id="rId20" display="https://is.slu.cz/auth/predmet/fpf/leto2024/UIIABP0045" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="B12" r:id="rId21" display="https://is.slu.cz/auth/predmet/fpf/leto2024/UIIABP0044" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="B11" r:id="rId22" display="https://is.slu.cz/auth/predmet/fpf/leto2024/UIIABP0042" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="B10" r:id="rId23" display="https://is.slu.cz/auth/predmet/fpf/leto2024/UIIABP0042" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="B9" r:id="rId24" display="https://is.slu.cz/auth/predmet/fpf/leto2024/UIIABP0041" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="B8" r:id="rId25" display="https://is.slu.cz/auth/predmet/fpf/zima2023/UIIABP0006" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="B7" r:id="rId26" display="https://is.slu.cz/auth/predmet/fpf/zima2023/UIIABP0003" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="B6" r:id="rId27" display="https://is.slu.cz/auth/predmet/fpf/zima2023/UIIABP0003" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="B5" r:id="rId28" display="https://is.slu.cz/auth/predmet/fpf/zima2023/UIIABP0003" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="B4" r:id="rId29" display="https://is.slu.cz/auth/predmet/fpf/zima2023/UIIABP0002" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId30"/>
@@ -2959,7 +2982,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3034,7 +3057,7 @@
       </c>
       <c r="J3" s="9" t="str">
         <f>COUNTIF(Tabulka220[Status],"Ano")&amp;" / "&amp;COUNTIF(Tabulka220[Status],"*")</f>
-        <v>1 / 4</v>
+        <v>0 / 4</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3056,8 +3079,8 @@
       <c r="F4" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>198</v>
+      <c r="G4" s="4" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3087,7 +3110,7 @@
       </c>
       <c r="J5" s="11" t="str">
         <f>SUMIFS(Tabulka220[Kredity], Tabulka220[Status],"Ano")&amp;" / "&amp;SUM(Tabulka220[Kredity])</f>
-        <v>5 / 21</v>
+        <v>0 / 21</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3109,8 +3132,8 @@
       <c r="F6" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>81</v>
+      <c r="G6" s="4" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25">
@@ -3174,14 +3197,14 @@
         <v>84</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="I16" t="s">
         <v>91</v>
       </c>
       <c r="J16" s="9" t="str">
         <f>COUNTIF(Tabulka321[Status],"Ano")&amp;" / "&amp;COUNTIF(Tabulka321[Status],"*")</f>
-        <v>2 / 3</v>
+        <v>0 / 3</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
@@ -3227,14 +3250,14 @@
         <v>85</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="I18" s="10" t="s">
         <v>110</v>
       </c>
       <c r="J18" s="11" t="str">
         <f>SUMIFS(Tabulka321[Kredity], Tabulka321[Status],"Ano")&amp;" / "&amp;SUM(Tabulka321[Kredity])</f>
-        <v>6 / 9</v>
+        <v>0 / 9</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -3243,30 +3266,31 @@
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A14:G14"/>
   </mergeCells>
+  <phoneticPr fontId="7" type="noConversion"/>
+  <conditionalFormatting sqref="A3:G6">
+    <cfRule type="expression" dxfId="9" priority="1">
+      <formula>$G3="Dělám"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="8" priority="2">
+      <formula>$G3="Ano"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A16:G18">
-    <cfRule type="expression" dxfId="44" priority="3">
+    <cfRule type="expression" dxfId="7" priority="3">
       <formula>$G16="Dělám"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="43" priority="4">
+    <cfRule type="expression" dxfId="6" priority="4">
       <formula>$G16="Ano"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A3:G6">
-    <cfRule type="expression" dxfId="42" priority="1">
-      <formula>$G3="Dělám"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="41" priority="2">
-      <formula>$G3="Ano"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="B3" r:id="rId1" display="https://is.slu.cz/auth/predmet/fpf/zima2024/UIIABP0021"/>
-    <hyperlink ref="B4" r:id="rId2" display="https://is.slu.cz/auth/predmet/fpf/zima2024/UIIABP0022"/>
-    <hyperlink ref="B5" r:id="rId3" display="https://is.slu.cz/auth/predmet/fpf/zima2024/UIIABP0023"/>
-    <hyperlink ref="B6" r:id="rId4" display="https://is.slu.cz/auth/predmet/fpf/leto2024/UIIABP0058"/>
-    <hyperlink ref="B16" r:id="rId5" display="https://is.slu.cz/auth/predmet/fpf/zima2024/UIIABP0024"/>
-    <hyperlink ref="B17" r:id="rId6" display="https://is.slu.cz/auth/predmet/fpf/zima2023/UIIABP0025"/>
-    <hyperlink ref="B18" r:id="rId7" display="https://is.slu.cz/auth/predmet/fpf/zima2024/UIIABP0059"/>
+    <hyperlink ref="B3" r:id="rId1" display="https://is.slu.cz/auth/predmet/fpf/zima2024/UIIABP0021" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="B4" r:id="rId2" display="https://is.slu.cz/auth/predmet/fpf/zima2024/UIIABP0022" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
+    <hyperlink ref="B5" r:id="rId3" display="https://is.slu.cz/auth/predmet/fpf/zima2024/UIIABP0023" xr:uid="{00000000-0004-0000-0100-000002000000}"/>
+    <hyperlink ref="B6" r:id="rId4" display="https://is.slu.cz/auth/predmet/fpf/leto2024/UIIABP0058" xr:uid="{00000000-0004-0000-0100-000003000000}"/>
+    <hyperlink ref="B16" r:id="rId5" display="https://is.slu.cz/auth/predmet/fpf/zima2024/UIIABP0024" xr:uid="{00000000-0004-0000-0100-000004000000}"/>
+    <hyperlink ref="B17" r:id="rId6" display="https://is.slu.cz/auth/predmet/fpf/zima2023/UIIABP0025" xr:uid="{00000000-0004-0000-0100-000005000000}"/>
+    <hyperlink ref="B18" r:id="rId7" display="https://is.slu.cz/auth/predmet/fpf/zima2024/UIIABP0059" xr:uid="{00000000-0004-0000-0100-000006000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <tableParts count="2">
@@ -3277,7 +3301,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:J67"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3344,7 +3368,7 @@
       <c r="F3" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="3" t="s">
         <v>81</v>
       </c>
       <c r="I3" s="12" t="s">
@@ -3375,7 +3399,7 @@
         <v>83</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>81</v>
+        <v>198</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3397,7 +3421,7 @@
       <c r="F5" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="3" t="s">
         <v>87</v>
       </c>
       <c r="I5" s="1" t="s">
@@ -3474,7 +3498,7 @@
         <v>88</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -3536,14 +3560,14 @@
         <v>86</v>
       </c>
       <c r="G16" t="s">
-        <v>81</v>
+        <v>198</v>
       </c>
       <c r="I16" t="s">
         <v>91</v>
       </c>
       <c r="J16" s="9" t="str">
         <f>COUNTIF(Tabulka220245[Status],"Ano")&amp;" / "&amp;COUNTIF(Tabulka220245[Status],"*")</f>
-        <v>2 / 5</v>
+        <v>0 / 5</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3596,7 +3620,7 @@
       </c>
       <c r="J18" s="11" t="str">
         <f>SUMIFS(Tabulka220245[Kredity], Tabulka220245[Status],"Ano")&amp;" / "&amp;SUM(Tabulka220245[Kredity])</f>
-        <v>4 / 12</v>
+        <v>0 / 12</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -3619,7 +3643,7 @@
         <v>85</v>
       </c>
       <c r="G19" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -3699,14 +3723,14 @@
         <v>85</v>
       </c>
       <c r="G28" t="s">
-        <v>87</v>
+        <v>198</v>
       </c>
       <c r="I28" t="s">
         <v>91</v>
       </c>
       <c r="J28" s="9" t="str">
         <f>COUNTIF(Tabulka2202456[Status],"Ano")&amp;" / "&amp;COUNTIF(Tabulka2202456[Status],"*")</f>
-        <v>2 / 11</v>
+        <v>0 / 11</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3759,7 +3783,7 @@
       </c>
       <c r="J30" s="11" t="str">
         <f>SUMIFS(Tabulka2202456[Kredity], Tabulka2202456[Status],"Ano")&amp;" / "&amp;SUM(Tabulka2202456[Kredity])</f>
-        <v>4 / 25</v>
+        <v>0 / 25</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3920,7 +3944,7 @@
         <v>88</v>
       </c>
       <c r="G37" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3942,8 +3966,8 @@
       <c r="F38" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="G38" s="13" t="s">
-        <v>81</v>
+      <c r="G38" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -4000,14 +4024,14 @@
         <v>85</v>
       </c>
       <c r="G46" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="I46" t="s">
         <v>91</v>
       </c>
       <c r="J46" s="9" t="str">
         <f>COUNTIF(Tabulka2202457[Status],"Ano")&amp;" / "&amp;COUNTIF(Tabulka2202457[Status],"*")</f>
-        <v>1 / 4</v>
+        <v>2 / 4</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4030,7 +4054,7 @@
         <v>85</v>
       </c>
       <c r="G47" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4083,7 +4107,7 @@
         <v>85</v>
       </c>
       <c r="G49" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="50" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -4374,67 +4398,68 @@
     <mergeCell ref="A44:G44"/>
     <mergeCell ref="A55:G55"/>
   </mergeCells>
+  <phoneticPr fontId="7" type="noConversion"/>
   <conditionalFormatting sqref="A3:G8 A46:G49 A57:G66">
-    <cfRule type="expression" dxfId="30" priority="11">
+    <cfRule type="expression" dxfId="5" priority="11">
       <formula>$G3="Ano"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="29" priority="12">
+    <cfRule type="expression" dxfId="4" priority="12">
       <formula>$G3="Dělám"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A16:G20">
-    <cfRule type="expression" dxfId="28" priority="7">
+    <cfRule type="expression" dxfId="3" priority="7">
       <formula>$G16="Ano"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="27" priority="8">
+    <cfRule type="expression" dxfId="2" priority="8">
       <formula>$G16="Dělám"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A28:G38">
-    <cfRule type="expression" dxfId="26" priority="5">
+    <cfRule type="expression" dxfId="1" priority="5">
       <formula>$G28="Ano"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="25" priority="6">
+    <cfRule type="expression" dxfId="0" priority="6">
       <formula>$G28="Dělám"</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="B3" r:id="rId1" display="https://is.slu.cz/auth/predmet/fpf/zima2023/UIIABP0026"/>
-    <hyperlink ref="B4" r:id="rId2" display="https://is.slu.cz/auth/predmet/fpf/zima2024/UIIABP0027"/>
-    <hyperlink ref="B5" r:id="rId3" display="https://is.slu.cz/auth/predmet/fpf/leto2024/UIIABP0060"/>
-    <hyperlink ref="B8" r:id="rId4" display="https://is.slu.cz/auth/predmet/fpf/leto2024/UIINP00001"/>
-    <hyperlink ref="B7" r:id="rId5" display="https://is.slu.cz/auth/predmet/fpf/leto2024/UIIABP0062"/>
-    <hyperlink ref="B6" r:id="rId6" display="https://is.slu.cz/auth/predmet/fpf/leto2024/UIIABP0061"/>
-    <hyperlink ref="B16" r:id="rId7"/>
-    <hyperlink ref="B17" r:id="rId8"/>
-    <hyperlink ref="B18" r:id="rId9"/>
-    <hyperlink ref="B19" r:id="rId10"/>
-    <hyperlink ref="B20" r:id="rId11"/>
-    <hyperlink ref="B28" r:id="rId12"/>
-    <hyperlink ref="B29" r:id="rId13"/>
-    <hyperlink ref="B30" r:id="rId14"/>
-    <hyperlink ref="B31" r:id="rId15"/>
-    <hyperlink ref="B32" r:id="rId16"/>
-    <hyperlink ref="B33" r:id="rId17"/>
-    <hyperlink ref="B34" r:id="rId18"/>
-    <hyperlink ref="B35" r:id="rId19"/>
-    <hyperlink ref="B36" r:id="rId20"/>
-    <hyperlink ref="B37" r:id="rId21"/>
-    <hyperlink ref="B38" r:id="rId22"/>
-    <hyperlink ref="B46" r:id="rId23"/>
-    <hyperlink ref="B47" r:id="rId24"/>
-    <hyperlink ref="B48" r:id="rId25"/>
-    <hyperlink ref="B49" r:id="rId26"/>
-    <hyperlink ref="B57" r:id="rId27"/>
-    <hyperlink ref="B58" r:id="rId28"/>
-    <hyperlink ref="B59" r:id="rId29"/>
-    <hyperlink ref="B60" r:id="rId30"/>
-    <hyperlink ref="B61" r:id="rId31"/>
-    <hyperlink ref="B62" r:id="rId32"/>
-    <hyperlink ref="B63" r:id="rId33"/>
-    <hyperlink ref="B64" r:id="rId34"/>
-    <hyperlink ref="B65" r:id="rId35"/>
-    <hyperlink ref="B66" r:id="rId36"/>
+    <hyperlink ref="B3" r:id="rId1" display="https://is.slu.cz/auth/predmet/fpf/zima2023/UIIABP0026" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
+    <hyperlink ref="B4" r:id="rId2" display="https://is.slu.cz/auth/predmet/fpf/zima2024/UIIABP0027" xr:uid="{00000000-0004-0000-0200-000001000000}"/>
+    <hyperlink ref="B5" r:id="rId3" display="https://is.slu.cz/auth/predmet/fpf/leto2024/UIIABP0060" xr:uid="{00000000-0004-0000-0200-000002000000}"/>
+    <hyperlink ref="B8" r:id="rId4" display="https://is.slu.cz/auth/predmet/fpf/leto2024/UIINP00001" xr:uid="{00000000-0004-0000-0200-000003000000}"/>
+    <hyperlink ref="B7" r:id="rId5" display="https://is.slu.cz/auth/predmet/fpf/leto2024/UIIABP0062" xr:uid="{00000000-0004-0000-0200-000004000000}"/>
+    <hyperlink ref="B6" r:id="rId6" display="https://is.slu.cz/auth/predmet/fpf/leto2024/UIIABP0061" xr:uid="{00000000-0004-0000-0200-000005000000}"/>
+    <hyperlink ref="B16" r:id="rId7" xr:uid="{00000000-0004-0000-0200-000006000000}"/>
+    <hyperlink ref="B17" r:id="rId8" xr:uid="{00000000-0004-0000-0200-000007000000}"/>
+    <hyperlink ref="B18" r:id="rId9" xr:uid="{00000000-0004-0000-0200-000008000000}"/>
+    <hyperlink ref="B19" r:id="rId10" xr:uid="{00000000-0004-0000-0200-000009000000}"/>
+    <hyperlink ref="B20" r:id="rId11" xr:uid="{00000000-0004-0000-0200-00000A000000}"/>
+    <hyperlink ref="B28" r:id="rId12" xr:uid="{00000000-0004-0000-0200-00000B000000}"/>
+    <hyperlink ref="B29" r:id="rId13" xr:uid="{00000000-0004-0000-0200-00000C000000}"/>
+    <hyperlink ref="B30" r:id="rId14" xr:uid="{00000000-0004-0000-0200-00000D000000}"/>
+    <hyperlink ref="B31" r:id="rId15" xr:uid="{00000000-0004-0000-0200-00000E000000}"/>
+    <hyperlink ref="B32" r:id="rId16" xr:uid="{00000000-0004-0000-0200-00000F000000}"/>
+    <hyperlink ref="B33" r:id="rId17" xr:uid="{00000000-0004-0000-0200-000010000000}"/>
+    <hyperlink ref="B34" r:id="rId18" xr:uid="{00000000-0004-0000-0200-000011000000}"/>
+    <hyperlink ref="B35" r:id="rId19" xr:uid="{00000000-0004-0000-0200-000012000000}"/>
+    <hyperlink ref="B36" r:id="rId20" xr:uid="{00000000-0004-0000-0200-000013000000}"/>
+    <hyperlink ref="B37" r:id="rId21" xr:uid="{00000000-0004-0000-0200-000014000000}"/>
+    <hyperlink ref="B38" r:id="rId22" xr:uid="{00000000-0004-0000-0200-000015000000}"/>
+    <hyperlink ref="B46" r:id="rId23" xr:uid="{00000000-0004-0000-0200-000016000000}"/>
+    <hyperlink ref="B47" r:id="rId24" xr:uid="{00000000-0004-0000-0200-000017000000}"/>
+    <hyperlink ref="B48" r:id="rId25" xr:uid="{00000000-0004-0000-0200-000018000000}"/>
+    <hyperlink ref="B49" r:id="rId26" xr:uid="{00000000-0004-0000-0200-000019000000}"/>
+    <hyperlink ref="B57" r:id="rId27" xr:uid="{00000000-0004-0000-0200-00001A000000}"/>
+    <hyperlink ref="B58" r:id="rId28" xr:uid="{00000000-0004-0000-0200-00001B000000}"/>
+    <hyperlink ref="B59" r:id="rId29" xr:uid="{00000000-0004-0000-0200-00001C000000}"/>
+    <hyperlink ref="B60" r:id="rId30" xr:uid="{00000000-0004-0000-0200-00001D000000}"/>
+    <hyperlink ref="B61" r:id="rId31" xr:uid="{00000000-0004-0000-0200-00001E000000}"/>
+    <hyperlink ref="B62" r:id="rId32" xr:uid="{00000000-0004-0000-0200-00001F000000}"/>
+    <hyperlink ref="B63" r:id="rId33" xr:uid="{00000000-0004-0000-0200-000020000000}"/>
+    <hyperlink ref="B64" r:id="rId34" xr:uid="{00000000-0004-0000-0200-000021000000}"/>
+    <hyperlink ref="B65" r:id="rId35" xr:uid="{00000000-0004-0000-0200-000022000000}"/>
+    <hyperlink ref="B66" r:id="rId36" xr:uid="{00000000-0004-0000-0200-000023000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId37"/>
